--- a/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:12:31+00:00</t>
+    <t>2026-03-16T15:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>minimal-ruim</t>
+    <t>MinimalRuim</t>
   </si>
   <si>
     <t>Title</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:56:46+00:00</t>
+    <t>2026-03-16T15:58:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,16 +118,13 @@
     <t>Content</t>
   </si>
   <si>
-    <t>complete</t>
+    <t>fragment</t>
   </si>
   <si>
     <t>Supplements</t>
   </si>
   <si>
     <t>Count</t>
-  </si>
-  <si>
-    <t>19088</t>
   </si>
   <si>
     <t>Code</t>
@@ -535,9 +532,7 @@
       <c r="A22" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>37</v>
-      </c>
+      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -551,116 +546,116 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>22</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>45</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>47</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>60</v>
-      </c>
       <c r="D9" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -675,63 +670,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>62</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>63</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>68</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>70</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="D5" s="2"/>
     </row>

--- a/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:58:44+00:00</t>
+    <t>2026-03-16T16:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:04:23+00:00</t>
+    <t>2026-03-24T16:06:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
